--- a/Outputs/Scenarios/PtX_demand_DK_Methanol.xlsx
+++ b/Outputs/Scenarios/PtX_demand_DK_Methanol.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.0004952914075622283</v>
       </c>
       <c r="K16" t="n">
-        <v>0.00259780244551083</v>
+        <v>0.002877396064777138</v>
       </c>
     </row>
     <row r="17">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.004329670742518051</v>
+        <v>0.004047361794181274</v>
       </c>
     </row>
     <row r="19">
@@ -1481,7 +1481,7 @@
         <v>7.136310795228682e-06</v>
       </c>
       <c r="K28" t="n">
-        <v>0.00173186829700722</v>
+        <v>0.001734583626077689</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.0007332186289504282</v>
       </c>
       <c r="K30" t="n">
-        <v>0.01400067233614843</v>
+        <v>0.01550752234985518</v>
       </c>
     </row>
     <row r="31">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.02333445389358072</v>
+        <v>0.02181296980611438</v>
       </c>
     </row>
     <row r="33">
@@ -1999,7 +1999,7 @@
         <v>3.85904541552857e-05</v>
       </c>
       <c r="K42" t="n">
-        <v>0.009333781557432289</v>
+        <v>0.009348415631191879</v>
       </c>
     </row>
     <row r="43">
